--- a/formatpicker/data/delivery_formats.xlsx
+++ b/formatpicker/data/delivery_formats.xlsx
@@ -799,7 +799,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M15"/>
+  <dimension ref="A1:M18"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1804,6 +1804,207 @@
       <c r="M15" t="inlineStr">
         <is>
           <t>Wylie, Cultivating a Court's Data STORY, NCSC Trends in State Courts (2025), Fig. 2.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>INTERACT</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Interactive Report</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Digital &amp; interactive</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>The full story as a web page, with working data files alongside.</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Internal;Both;External</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Colleague;Expert;Trustee/Funder</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Inform/Explain;Support a Decision;Document/Archive</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Long</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>A reader who needs to work with the findings, not just read them.</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>A print-only audience, or a reader who will not open a file.</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>Report-length, on screen</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>Added from practice (2026); not in the Trends Fig. 2 tree.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>VIDEO</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Video or Documentary</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Outreach &amp; media</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>The story told on screen, for people who will never open a report.</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Both;External</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Novice;Generalist</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Raise Awareness;Inform/Explain;Persuade/Advocate</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>Reaching people where they already watch.</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Method, caveats, or a reader who needs the numbers.</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>2-20 minutes</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>Added from practice (2026); not in the Trends Fig. 2 tree.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>GUIDE</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>How-To Guide</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Written report</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Step-by-step instructions someone else can follow to repeat the work.</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Internal;Both;External</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Colleague;Expert</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Inform/Explain;Document/Archive</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>Helping another court or team repeat what worked, step by step.</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Findings or persuasion: it teaches the how, not the why.</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>5-15 pages</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>Added from practice (2026); not in the Trends Fig. 2 tree.</t>
         </is>
       </c>
     </row>
@@ -1897,7 +2098,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Nothing is stored. This sorts the formats from the Trends tree; it never hides one.</t>
+          <t>Nothing is stored. This sorts the formats from the Trends tree, plus three from practice; it never hides one.</t>
         </is>
       </c>
     </row>

--- a/formatpicker/data/delivery_formats.xlsx
+++ b/formatpicker/data/delivery_formats.xlsx
@@ -964,7 +964,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Generalist;Colleague;Trustee/Funder</t>
+          <t>Generalist;Colleague;Expert;Trustee/Funder</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">

--- a/formatpicker/data/delivery_formats.xlsx
+++ b/formatpicker/data/delivery_formats.xlsx
@@ -2038,7 +2038,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>A quick way to match a deliverable to your audience and goal.</t>
+          <t>Match the format to your audience, reach, and goal.</t>
         </is>
       </c>
     </row>
@@ -2062,7 +2062,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Which Format Fits Best?</t>
+          <t>No format is best for everything.</t>
         </is>
       </c>
     </row>
@@ -2098,7 +2098,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Nothing is stored. This sorts the formats from the Trends tree, plus three from practice; it never hides one.</t>
+          <t>Nothing you enter leaves your browser. Every format gets sorted, never hidden.</t>
         </is>
       </c>
     </row>

--- a/formatpicker/data/delivery_formats.xlsx
+++ b/formatpicker/data/delivery_formats.xlsx
@@ -2062,7 +2062,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>No format is best for everything.</t>
+          <t>There is no single best format, and that is the point.</t>
         </is>
       </c>
     </row>
@@ -2074,7 +2074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Say who you are trying to reach and what you want the work to do, and every delivery format sorts into three piles: the ones that fit, the ones that could work with a tweak, and the ones that are the wrong tool here and why.</t>
+          <t>One set of findings can become a two-page brief, a formal report, a dashboard, or a documentary, and the right choice turns on who it is for, how far it has to travel, and what you need it to do. Answer three questions and each format sorts into what fits, what could work with a tweak, and what is simply the wrong tool here.</t>
         </is>
       </c>
     </row>
@@ -2098,7 +2098,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Nothing you enter leaves your browser. Every format gets sorted, never hidden.</t>
+          <t>Nothing you enter leaves your browser, and nothing is hidden: the tool sorts the whole field and shows what it ruled out, with the reason on each.</t>
         </is>
       </c>
     </row>

--- a/formatpicker/data/delivery_formats.xlsx
+++ b/formatpicker/data/delivery_formats.xlsx
@@ -799,7 +799,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M18"/>
+  <dimension ref="A1:M22"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -2003,6 +2003,274 @@
         </is>
       </c>
       <c r="M18" t="inlineStr">
+        <is>
+          <t>Added from practice (2026); not in the Trends Fig. 2 tree.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>WORKSHOP</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Workshop</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Presentation</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>A hands-on working session where the group learns or decides by doing, with you facilitating.</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Internal;Both</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Generalist;Colleague;Expert</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Inform/Explain;Support a Decision</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>Building data literacy, walking a team through a method, or facilitating a session where the group works through the data with you.</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>A one-way announcement, or anything that must travel afterward without a facilitator.</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>Half a day to a full day, in person or small-group virtual.</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>Added from practice (2026); not in the Trends Fig. 2 tree.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>WEBINAR</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Webinar</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Presentation</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>A live online session that carries a talk to a broad, registered audience.</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Both;External</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Novice;Generalist;Colleague;Expert</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Inform/Explain;Raise Awareness</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>Reaching people across locations at once, introducing a topic, or presenting to partners and the public without travel.</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Deep hands-on work, or a small internal group a meeting would serve better.</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>45 to 60 minutes, live, often recorded.</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>Added from practice (2026); not in the Trends Fig. 2 tree.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>POSTER</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Research Poster</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Presentation</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>A single visual board that carries one finding at a conference or event.</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Both;External</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Generalist;Colleague;Expert</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Inform/Explain;Raise Awareness</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Short</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>Summarizing a study for a professional audience, or presenting where a full talk is not on offer.</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Detail-heavy reporting, or any audience that will not stand and read.</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>One board, roughly 36 by 48 inches.</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>Added from practice (2026); not in the Trends Fig. 2 tree.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>OPED</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Op-ed or Commentary</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Outreach &amp; media</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>A short authored argument placed in an outlet your audience already reads.</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>External</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Novice;Generalist</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Persuade/Advocate;Raise Awareness;Inform/Explain</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Short</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>Making a case in your own voice, or putting a finding in front of readers who will not seek out a report.</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Neutral documentation, or a full account of methods and caveats.</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>600 to 800 words.</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
         <is>
           <t>Added from practice (2026); not in the Trends Fig. 2 tree.</t>
         </is>

--- a/formatpicker/data/delivery_formats.xlsx
+++ b/formatpicker/data/delivery_formats.xlsx
@@ -2227,7 +2227,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>A short authored argument placed in an outlet your audience already reads.</t>
+          <t>A brief opinion piece that makes your case in your own voice, in a publication people already read.</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
